--- a/branches/examples/StructureDefinition-codeValueSet.xlsx
+++ b/branches/examples/StructureDefinition-codeValueSet.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:15:32+00:00</t>
+    <t>2025-02-19T10:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
